--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260701.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260701.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>89,084,000</t>
+          <t>74,190,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.49%</t>
+          <t>8.93%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>1,965,000</t>
+          <t>1,566,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.97%</t>
+          <t>4.84%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>9,195,000</t>
+          <t>8,139,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4.61%</t>
+          <t>3.81%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1,260,000</t>
+          <t>1,102,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>3,895,000</t>
+          <t>3,640,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
@@ -721,100 +721,100 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>8,402,000</t>
+          <t>8,474,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>力成科技</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>13,112,000</t>
+          <t>17,902,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>威剛科技</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>18,132,000</t>
+          <t>8,800,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.80%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>環球晶圓</t>
+          <t>力成科技</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>3,546,000</t>
+          <t>10,433,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.49%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>威剛科技</t>
+          <t>環球晶圓</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>8,719,000</t>
+          <t>2,819,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.55%</t>
+          <t>2.22%</t>
         </is>
       </c>
     </row>
@@ -831,364 +831,364 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>6,465,000</t>
+          <t>6,096,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>2,312,000</t>
+          <t>14,694,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>202607WTX</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>115/07台股期貨</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,164,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>202607WTX</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>115/07台股期貨</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>8,385,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>2.02%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>可成科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>14,694,000</t>
+          <t>13,846,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>可成科技</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>12,281,000</t>
+          <t>8,865,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>11,327,000</t>
+          <t>28,370,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>11,019,000</t>
+          <t>23,336,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>矽格股份</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>10,211,000</t>
+          <t>10,658,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>矽格股份</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>22,435,000</t>
+          <t>9,918,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>24,911,000</t>
+          <t>5,632,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.64%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>瑞昱半導</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>5,069,000</t>
+          <t>2,733,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>8,683,000</t>
+          <t>10,137,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>瑞昱半導</t>
+          <t>旭隼科技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,026,000</t>
+          <t>1,697,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>台灣大哥</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>2,419,000</t>
+          <t>15,684,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>廣達電腦</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>614,000</t>
+          <t>4,961,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>仁寶電腦</t>
+          <t>亞翔工程</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>39,882,000</t>
+          <t>1,823,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1205,760 +1205,760 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>6,594,000</t>
+          <t>7,798,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>中華電信</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,379,937,177</t>
+          <t>11,440,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>義隆電子</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>7,156,000</t>
+          <t>2,577,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>台灣大哥</t>
+          <t>崇越科技</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,525,000</t>
+          <t>2,951,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>廣達電腦</t>
+          <t>遠傳電信</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,640,000</t>
+          <t>15,164,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>旭隼科技</t>
+          <t>義隆電子</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>1,238,000</t>
+          <t>8,318,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>神達控股</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,878,000</t>
+          <t>16,059,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>3,079,000</t>
+          <t>1,878,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>6548</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>長華科技</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>15,012,000</t>
+          <t>6,819,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>亞翔工程</t>
+          <t>緯創資通</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,340,000</t>
+          <t>9,071,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>36,789,000</t>
+          <t>3,552,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>崇越科技</t>
+          <t>祥碩科技</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>2,174,000</t>
+          <t>980,000</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>中華電信</t>
+          <t>技嘉科技</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>8,376,000</t>
+          <t>4,207,000</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>遠傳電信</t>
+          <t>微星科技</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>11,106,000</t>
+          <t>9,744,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>12,798,000</t>
+          <t>1,406,457,177</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>緯創資通</t>
+          <t>信邦電子</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,666,000</t>
+          <t>4,161,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>祥碩科技</t>
+          <t>鴻海精密</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>722,000</t>
+          <t>5,587,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>技嘉科技</t>
+          <t>洋基工程</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>3,084,000</t>
+          <t>1,808,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>微星科技</t>
+          <t>元太科技</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>7,145,000</t>
+          <t>6,556,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>6548</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>神達控股</t>
+          <t>長華科技</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>11,809,000</t>
+          <t>15,012,000</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8069</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>元太科技</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>4,825,000</t>
+          <t>479,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>洋基工程</t>
+          <t>英業達股</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,335,000</t>
+          <t>17,924,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>信邦電子</t>
+          <t>精成科技</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>3,058,000</t>
+          <t>10,647,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>至上電子</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>34,521,000</t>
+          <t>12,032,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>原相科技</t>
+          <t>仁寶電腦</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>3,766,000</t>
+          <t>31,156,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>英業達股</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>13,106,000</t>
+          <t>36,892,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>精成科技</t>
+          <t>原相科技</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>7,798,000</t>
+          <t>4,285,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>至上電子</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>9,017,000</t>
+          <t>28,614,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
+          <t>0.65%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>頎邦科技</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>3,868,000</t>
+          <t>9,903,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>鴻海精密</t>
+          <t>致伸科技</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>3,184,000</t>
+          <t>10,725,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>2352</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>佳世達科</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>1,435,000</t>
+          <t>21,602,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>5469</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>致伸科技</t>
+          <t>瀚宇博德</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>9,088,000</t>
+          <t>7,715,000</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>長華電材</t>
+          <t>頎邦科技</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>10,493,000</t>
+          <t>2,952,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>0.40%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>瀚宇博德</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>5,570,000</t>
+          <t>1,096,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>2352</t>
+          <t>8070</t>
         </is>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>佳世達科</t>
+          <t>長華電材</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>13,234,000</t>
+          <t>11,555,000</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
@@ -1975,12 +1975,12 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>3,629,000</t>
+          <t>2,640,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>3,006,000</t>
+          <t>2,212,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -2019,12 +2019,12 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>3,861,000</t>
+          <t>2,919,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>595,000</t>
+          <t>422,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -2063,12 +2063,12 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>2,280,000</t>
+          <t>1,473,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -2085,12 +2085,12 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>1,371,000</t>
+          <t>764,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>1,877,000</t>
+          <t>1,081,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -2129,29 +2129,29 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>1,233,000</t>
+          <t>730,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>崑鼎綠能</t>
+          <t>是方電訊</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>8454</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>是方電訊</t>
+          <t>富邦媒體</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>160,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,22 +2185,22 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>8454</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>富邦媒體</t>
+          <t>崑鼎綠能</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>160,000</t>
+          <t>88,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.02%</t>
         </is>
       </c>
     </row>
@@ -2229,66 +2229,44 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>PB_NTD</t>
+          <t>PFUR_NTD</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES</t>
+          <t>PAYABLES FOR UNITS REDEEMED</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-443,810,040</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>-0.32%</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>PFUR_NTD</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>PAYABLES FOR UNITS REDEEMED</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>-351,481,410</t>
+          <t>-16,312,489,895</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>-0.25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>DA_NTD</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr">
-        <is>
-          <t>-15,329,800,525</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>-10.98%</t>
+          <t>-11.62%</t>
         </is>
       </c>
     </row>
